--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133486285</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133486285</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133486285</v>
+        <v>133477377</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>9420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100575</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartoxe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ceruchus chrysomelinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hochenwarth, 1785)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grankärret, Grankärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555536</v>
+        <v>555583</v>
       </c>
       <c r="R2" t="n">
-        <v>6337532</v>
+        <v>6337508</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I brunrötad granlåga. Skogen avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -774,6 +788,205 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133486285</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555536</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6337532</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133931467</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555497</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6337518</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133486285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,61 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133477377</v>
+        <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>9420</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100575</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartoxe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ceruchus chrysomelinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hochenwarth, 1785)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grankärret, Grankärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555583</v>
+        <v>555450</v>
       </c>
       <c r="R2" t="n">
-        <v>6337508</v>
+        <v>6337541</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I brunrötad granlåga. Skogen avverkningsanmäld.</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,16 +776,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133477377</t>
+          <t>https://artportalen.se/Sighting/136339668</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133486285</v>
+        <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grankärret, Grankärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555536</v>
+        <v>555497</v>
       </c>
       <c r="R3" t="n">
-        <v>6337532</v>
+        <v>6337531</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133486285</t>
+          <t>https://artportalen.se/Sighting/136343166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133931467</v>
+        <v>136342999</v>
       </c>
       <c r="B4" t="n">
-        <v>103764</v>
+        <v>5182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222004</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555497</v>
+        <v>555484</v>
       </c>
       <c r="R4" t="n">
-        <v>6337518</v>
+        <v>6337550</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +985,760 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136342999</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133477377</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9420</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100575</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ceruchus chrysomelinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hochenwarth, 1785)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555583</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6337508</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I brunrötad granlåga. Skogen avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477377</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136342299</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6289</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101520</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större flatbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Peltis grossa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kulevirke, Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6337628</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera kläckhål på björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342299</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133486285</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555536</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6337532</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133486285</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136340969</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58149</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6337550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340969</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136347451</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555480</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6337545</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347451</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133931467</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555497</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6337518</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133931467</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136347450</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555430</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6337556</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347450</t>
         </is>
       </c>
     </row>
@@ -1013,6 +1747,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136340969</v>
       </c>
       <c r="B8" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98393</v>
+        <v>98406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98406</v>
+        <v>98407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136340969</v>
       </c>
       <c r="B8" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98407</v>
+        <v>98420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
